--- a/Donnees/Statistiques Démographiques et sociales/Education/Taux Net de Scolarisation 2006-2023.xlsx
+++ b/Donnees/Statistiques Démographiques et sociales/Education/Taux Net de Scolarisation 2006-2023.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hp\Desktop\2025\Annuaire des Statistiques Socio-démographiques_Edition 2025_VP\Atelier de Finalisation et Validation de l'Annuaire 2025\Portail DSDSG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\Ansade_Project\Donnees\Statistiques Démographiques et sociales\Education\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B130E7DA-D2D1-4DD2-B6FE-5A8641D6E682}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{629B80E4-447C-40EE-9513-807C541E49AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Garçons" sheetId="4" r:id="rId1"/>
@@ -22,14 +22,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -112,28 +104,6 @@
     <t>Wilaya</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Source:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve"> Annuaires des Statistiques Scolaires</t>
-    </r>
-  </si>
-  <si>
     <t>64.8</t>
   </si>
   <si>
@@ -533,79 +503,16 @@
     <t>78,17</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Tableau</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>: Evolution du Taux Net de Scolarisation (TNS) au Fondamental pour les Garçons par Wilaya durant la période 2006-2023</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Tableau</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: Evolution du Taux Net de Scolarisation (TNS) au Fondamental pour les filles par Wilaya, durant la période 2006-2023 </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <u/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Tableau</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">: Evolution du Taux Net de Scolarisation (TNS) au Fondamental pour les deux sexes par Wilaya, durant la période 2006-2023 </t>
-    </r>
+    <t>Tableau 1.2.4: Evolution du Taux Net de Scolarisation (TNS) au Fondamental pour les Garçons par Wilaya durant la période 2006-2023</t>
+  </si>
+  <si>
+    <t>Source : MENRSE, Annuaires des Statistiques Scolaires</t>
+  </si>
+  <si>
+    <t>Tableau 1.2.5: Evolution du Taux Net de Scolarisation (TNS) au Fondamental pour les filles par Wilaya, durant la période 2006-2023</t>
+  </si>
+  <si>
+    <t>Tableau 1.2.6: Evolution du Taux Net de Scolarisation (TNS) au Fondamental pour les deux sexes par Wilaya, durant la période 2006-2023</t>
   </si>
 </sst>
 </file>
@@ -799,7 +706,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -824,9 +731,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -853,6 +757,10 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1136,26 +1044,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26EDA8B0-80D3-44A1-8AD1-832530504FBD}">
   <dimension ref="A1:I17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.81640625" customWidth="1"/>
-    <col min="2" max="2" width="10.90625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.08984375" customWidth="1"/>
-    <col min="4" max="4" width="12.1796875" customWidth="1"/>
-    <col min="5" max="5" width="12.08984375" customWidth="1"/>
-    <col min="6" max="6" width="11.6328125" customWidth="1"/>
-    <col min="7" max="7" width="10.81640625" customWidth="1"/>
-    <col min="8" max="8" width="17.36328125" customWidth="1"/>
-    <col min="9" max="9" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.77734375" customWidth="1"/>
+    <col min="2" max="2" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.109375" customWidth="1"/>
+    <col min="4" max="4" width="12.21875" customWidth="1"/>
+    <col min="5" max="5" width="12.109375" customWidth="1"/>
+    <col min="6" max="6" width="11.6640625" customWidth="1"/>
+    <col min="7" max="7" width="10.77734375" customWidth="1"/>
+    <col min="8" max="8" width="17.33203125" customWidth="1"/>
+    <col min="9" max="9" width="10.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="9" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="18" t="s">
+    <row r="1" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="19" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="17" t="s">
         <v>24</v>
       </c>
       <c r="B2" s="8" t="s">
@@ -1183,415 +1091,415 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="F3" s="13">
+      <c r="B3" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>127</v>
+      </c>
+      <c r="F3" s="12">
         <v>76.62</v>
       </c>
-      <c r="G3" s="14">
+      <c r="G3" s="13">
         <v>74.03</v>
       </c>
-      <c r="H3" s="14">
+      <c r="H3" s="13">
         <v>73.5</v>
       </c>
-      <c r="I3" s="14">
+      <c r="I3" s="13">
         <v>71.13</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="19.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="F4" s="14">
+      <c r="B4" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="F4" s="13">
         <v>83.7</v>
       </c>
-      <c r="G4" s="14">
+      <c r="G4" s="13">
         <v>82.76</v>
       </c>
-      <c r="H4" s="14">
+      <c r="H4" s="13">
         <v>75.989999999999995</v>
       </c>
-      <c r="I4" s="14">
+      <c r="I4" s="13">
         <v>78.569999999999993</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="27" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="E5" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="F5" s="14">
+      <c r="B5" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="E5" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="F5" s="13">
         <v>74.48</v>
       </c>
-      <c r="G5" s="14">
+      <c r="G5" s="13">
         <v>72.63</v>
       </c>
-      <c r="H5" s="14">
+      <c r="H5" s="13">
         <v>72.349999999999994</v>
       </c>
-      <c r="I5" s="14">
+      <c r="I5" s="13">
         <v>70.19</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="27" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="D6" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="F6" s="14">
+      <c r="B6" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="F6" s="13">
         <v>72.11</v>
       </c>
-      <c r="G6" s="14">
+      <c r="G6" s="13">
         <v>72.91</v>
       </c>
-      <c r="H6" s="14">
+      <c r="H6" s="13">
         <v>68.290000000000006</v>
       </c>
-      <c r="I6" s="14">
+      <c r="I6" s="13">
         <v>70.290000000000006</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="27" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="E7" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="F7" s="14">
+      <c r="B7" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="F7" s="13">
         <v>90.6</v>
       </c>
-      <c r="G7" s="14">
+      <c r="G7" s="13">
         <v>86.27</v>
       </c>
-      <c r="H7" s="14">
+      <c r="H7" s="13">
         <v>85.29</v>
       </c>
-      <c r="I7" s="14">
+      <c r="I7" s="13">
         <v>86.89</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="27" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="D8" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="E8" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="F8" s="14">
+      <c r="B8" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="F8" s="13">
         <v>86.22</v>
       </c>
-      <c r="G8" s="14">
+      <c r="G8" s="13">
         <v>87</v>
       </c>
-      <c r="H8" s="14">
+      <c r="H8" s="13">
         <v>85.55</v>
       </c>
-      <c r="I8" s="14">
+      <c r="I8" s="13">
         <v>81.489999999999995</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="27" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="F9" s="14">
+      <c r="B9" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="F9" s="13">
         <v>112.27</v>
       </c>
-      <c r="G9" s="14">
+      <c r="G9" s="13">
         <v>116.13</v>
       </c>
-      <c r="H9" s="14">
+      <c r="H9" s="13">
         <v>114.37</v>
       </c>
-      <c r="I9" s="14">
+      <c r="I9" s="13">
         <v>120.08</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="27" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="D10" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="F10" s="14">
+      <c r="B10" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="F10" s="13">
         <v>85.37</v>
       </c>
-      <c r="G10" s="14">
+      <c r="G10" s="13">
         <v>82.66</v>
       </c>
-      <c r="H10" s="14">
+      <c r="H10" s="13">
         <v>83.08</v>
       </c>
-      <c r="I10" s="14">
+      <c r="I10" s="13">
         <v>75.94</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="27" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B11" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="F11" s="14">
+      <c r="B11" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>111</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="F11" s="13">
         <v>85.17</v>
       </c>
-      <c r="G11" s="14">
+      <c r="G11" s="13">
         <v>84.17</v>
       </c>
-      <c r="H11" s="14">
+      <c r="H11" s="13">
         <v>83.29</v>
       </c>
-      <c r="I11" s="14">
+      <c r="I11" s="13">
         <v>85.26</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="27" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="D12" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="F12" s="14">
+      <c r="B12" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="F12" s="13">
         <v>88.99</v>
       </c>
-      <c r="G12" s="14">
+      <c r="G12" s="13">
         <v>83.75</v>
       </c>
-      <c r="H12" s="14">
+      <c r="H12" s="13">
         <v>83.33</v>
       </c>
-      <c r="I12" s="14">
+      <c r="I12" s="13">
         <v>81.48</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="D13" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="F13" s="14">
+      <c r="B13" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>134</v>
+      </c>
+      <c r="F13" s="13">
         <v>88.28</v>
       </c>
-      <c r="G13" s="14">
+      <c r="G13" s="13">
         <v>83.51</v>
       </c>
-      <c r="H13" s="14">
+      <c r="H13" s="13">
         <v>85.58</v>
       </c>
-      <c r="I13" s="14">
+      <c r="I13" s="13">
         <v>84.27</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="27" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="D14" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="F14" s="14">
+      <c r="B14" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>135</v>
+      </c>
+      <c r="F14" s="13">
         <v>100.27</v>
       </c>
-      <c r="G14" s="14">
+      <c r="G14" s="13">
         <v>89.48</v>
       </c>
-      <c r="H14" s="14">
+      <c r="H14" s="13">
         <v>89.84</v>
       </c>
-      <c r="I14" s="14">
+      <c r="I14" s="13">
         <v>89.06</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="27" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="F15" s="14">
+      <c r="B15" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="F15" s="13">
         <v>90.79</v>
       </c>
-      <c r="G15" s="14">
+      <c r="G15" s="13">
         <v>84.25</v>
       </c>
-      <c r="H15" s="14">
+      <c r="H15" s="13">
         <v>83.61</v>
       </c>
-      <c r="I15" s="14">
+      <c r="I15" s="13">
         <v>80.2</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="27" x14ac:dyDescent="0.35">
-      <c r="A16" s="12" t="s">
+    <row r="16" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A16" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="C16" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="D16" s="15" t="s">
-        <v>126</v>
-      </c>
-      <c r="E16" s="15" t="s">
-        <v>126</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>151</v>
-      </c>
-      <c r="G16" s="16" t="s">
-        <v>153</v>
-      </c>
-      <c r="H16" s="16" t="s">
-        <v>155</v>
-      </c>
-      <c r="I16" s="16" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="10" t="s">
-        <v>25</v>
+      <c r="B16" s="14" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="E16" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="F16" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="H16" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="I16" s="15" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="20" t="s">
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -1604,21 +1512,21 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C40D9C6B-8B5F-43D6-B8D8-03B871EC205E}">
   <dimension ref="A1:I17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.54296875" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5546875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="22.36328125" style="1" customWidth="1"/>
-    <col min="2" max="5" width="11.54296875" style="1"/>
-    <col min="6" max="6" width="11.54296875" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="11.54296875" style="1"/>
+    <col min="1" max="1" width="22.33203125" style="1" customWidth="1"/>
+    <col min="2" max="5" width="11.5546875" style="1"/>
+    <col min="6" max="6" width="11.5546875" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="11.5546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="19" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="15.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="18" t="s">
+    <row r="2" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="17" t="s">
         <v>24</v>
       </c>
       <c r="B2" s="5" t="s">
@@ -1646,415 +1554,415 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="27" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="F3" s="13">
+      <c r="B3" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="F3" s="12">
         <v>73.989999999999995</v>
       </c>
-      <c r="G3" s="14">
+      <c r="G3" s="13">
         <v>71.66</v>
       </c>
-      <c r="H3" s="14">
+      <c r="H3" s="13">
         <v>68.16</v>
       </c>
-      <c r="I3" s="14">
+      <c r="I3" s="13">
         <v>67.78</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="27" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>100</v>
-      </c>
-      <c r="E4" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="F4" s="14">
+      <c r="B4" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="F4" s="13">
         <v>79.05</v>
       </c>
-      <c r="G4" s="14">
+      <c r="G4" s="13">
         <v>75.92</v>
       </c>
-      <c r="H4" s="14">
+      <c r="H4" s="13">
         <v>79.67</v>
       </c>
-      <c r="I4" s="14">
+      <c r="I4" s="13">
         <v>75.2</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="27" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>103</v>
-      </c>
-      <c r="E5" s="14">
+      <c r="B5" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="E5" s="13">
         <v>71.3</v>
       </c>
-      <c r="F5" s="14">
+      <c r="F5" s="13">
         <v>80.959999999999994</v>
       </c>
-      <c r="G5" s="14">
+      <c r="G5" s="13">
         <v>77.819999999999993</v>
       </c>
-      <c r="H5" s="14">
+      <c r="H5" s="13">
         <v>74.03</v>
       </c>
-      <c r="I5" s="14">
+      <c r="I5" s="13">
         <v>73.44</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="27" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="F6" s="14">
+      <c r="B6" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>137</v>
+      </c>
+      <c r="F6" s="13">
         <v>74.45</v>
       </c>
-      <c r="G6" s="14">
+      <c r="G6" s="13">
         <v>69.87</v>
       </c>
-      <c r="H6" s="14">
+      <c r="H6" s="13">
         <v>71.81</v>
       </c>
-      <c r="I6" s="14">
+      <c r="I6" s="13">
         <v>68.010000000000005</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="27" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="14" t="s">
-        <v>38</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="F7" s="14">
+      <c r="B7" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="F7" s="13">
         <v>88.18</v>
       </c>
-      <c r="G7" s="14">
+      <c r="G7" s="13">
         <v>89.49</v>
       </c>
-      <c r="H7" s="14">
+      <c r="H7" s="13">
         <v>88.37</v>
       </c>
-      <c r="I7" s="14">
+      <c r="I7" s="13">
         <v>85.91</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="27" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="14" t="s">
-        <v>41</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="E8" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="F8" s="14">
+      <c r="B8" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="F8" s="13">
         <v>91.96</v>
       </c>
-      <c r="G8" s="14">
+      <c r="G8" s="13">
         <v>86.55</v>
       </c>
-      <c r="H8" s="14">
+      <c r="H8" s="13">
         <v>84.59</v>
       </c>
-      <c r="I8" s="14">
+      <c r="I8" s="13">
         <v>86.83</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="27" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="E9" s="14">
+      <c r="B9" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="E9" s="13">
         <v>62.2</v>
       </c>
-      <c r="F9" s="14">
+      <c r="F9" s="13">
         <v>116.35</v>
       </c>
-      <c r="G9" s="14">
+      <c r="G9" s="13">
         <v>110.72</v>
       </c>
-      <c r="H9" s="14">
+      <c r="H9" s="13">
         <v>112.19</v>
       </c>
-      <c r="I9" s="14">
+      <c r="I9" s="13">
         <v>107.83</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="F10" s="14">
+      <c r="B10" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="F10" s="13">
         <v>88.01</v>
       </c>
-      <c r="G10" s="14">
+      <c r="G10" s="13">
         <v>85.05</v>
       </c>
-      <c r="H10" s="14">
+      <c r="H10" s="13">
         <v>79.91</v>
       </c>
-      <c r="I10" s="14">
+      <c r="I10" s="13">
         <v>84.2</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="27" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B11" s="14" t="s">
-        <v>48</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>84</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>113</v>
-      </c>
-      <c r="E11" s="14" t="s">
-        <v>142</v>
-      </c>
-      <c r="F11" s="14">
+      <c r="B11" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="F11" s="13">
         <v>85.69</v>
       </c>
-      <c r="G11" s="14">
+      <c r="G11" s="13">
         <v>83.89</v>
       </c>
-      <c r="H11" s="14">
+      <c r="H11" s="13">
         <v>82.96</v>
       </c>
-      <c r="I11" s="14">
+      <c r="I11" s="13">
         <v>80.39</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="27" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="14" t="s">
-        <v>50</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>86</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="E12" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="F12" s="14">
+      <c r="B12" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>140</v>
+      </c>
+      <c r="F12" s="13">
         <v>93.1</v>
       </c>
-      <c r="G12" s="14">
+      <c r="G12" s="13">
         <v>92.71</v>
       </c>
-      <c r="H12" s="14">
+      <c r="H12" s="13">
         <v>88.34</v>
       </c>
-      <c r="I12" s="14">
+      <c r="I12" s="13">
         <v>86.97</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="27" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>143</v>
-      </c>
-      <c r="F13" s="14">
+      <c r="B13" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>142</v>
+      </c>
+      <c r="F13" s="13">
         <v>79.98</v>
       </c>
-      <c r="G13" s="14">
+      <c r="G13" s="13">
         <v>81.69</v>
       </c>
-      <c r="H13" s="14">
+      <c r="H13" s="13">
         <v>77.45</v>
       </c>
-      <c r="I13" s="14">
+      <c r="I13" s="13">
         <v>77.959999999999994</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="27" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="E14" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="F14" s="14">
+      <c r="B14" s="13" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="F14" s="13">
         <v>81.27</v>
       </c>
-      <c r="G14" s="14">
+      <c r="G14" s="13">
         <v>84.13</v>
       </c>
-      <c r="H14" s="14">
+      <c r="H14" s="13">
         <v>78.209999999999994</v>
       </c>
-      <c r="I14" s="14">
+      <c r="I14" s="13">
         <v>74.63</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="27" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="14" t="s">
-        <v>57</v>
-      </c>
-      <c r="C15" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="D15" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="E15" s="14">
+      <c r="B15" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="E15" s="13">
         <v>75.599999999999994</v>
       </c>
-      <c r="F15" s="14">
+      <c r="F15" s="13">
         <v>87.65</v>
       </c>
-      <c r="G15" s="14">
+      <c r="G15" s="13">
         <v>87.04</v>
       </c>
-      <c r="H15" s="14">
+      <c r="H15" s="13">
         <v>81.34</v>
       </c>
-      <c r="I15" s="14">
+      <c r="I15" s="13">
         <v>80.13</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="27" x14ac:dyDescent="0.35">
-      <c r="A16" s="12" t="s">
+    <row r="16" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A16" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="C16" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="D16" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="E16" s="16">
+      <c r="B16" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="E16" s="15">
         <v>75.2</v>
       </c>
-      <c r="F16" s="16" t="s">
-        <v>152</v>
-      </c>
-      <c r="G16" s="16" t="s">
-        <v>154</v>
-      </c>
-      <c r="H16" s="16" t="s">
-        <v>156</v>
-      </c>
-      <c r="I16" s="16" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A17" s="10" t="s">
-        <v>25</v>
+      <c r="F16" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="G16" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="H16" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="I16" s="15" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="20" t="s">
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -2066,21 +1974,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6EC6352-EA11-4F17-8AF6-AD1C5672D00E}">
   <dimension ref="A1:I17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.54296875" customWidth="1"/>
-    <col min="2" max="2" width="13.81640625" customWidth="1"/>
-    <col min="3" max="3" width="14.36328125" customWidth="1"/>
-    <col min="4" max="4" width="13.453125" customWidth="1"/>
-    <col min="5" max="5" width="13.6328125" customWidth="1"/>
-    <col min="6" max="6" width="12.08984375" customWidth="1"/>
-    <col min="7" max="7" width="11.453125" customWidth="1"/>
-    <col min="8" max="8" width="10.90625" customWidth="1"/>
-    <col min="9" max="9" width="10.81640625" customWidth="1"/>
+    <col min="1" max="1" width="16.5546875" customWidth="1"/>
+    <col min="2" max="2" width="13.77734375" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" customWidth="1"/>
+    <col min="4" max="4" width="13.44140625" customWidth="1"/>
+    <col min="5" max="5" width="13.6640625" customWidth="1"/>
+    <col min="6" max="6" width="12.109375" customWidth="1"/>
+    <col min="7" max="7" width="11.44140625" customWidth="1"/>
+    <col min="8" max="8" width="10.88671875" customWidth="1"/>
+    <col min="9" max="9" width="10.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="9" t="s">
+    <row r="1" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="19" t="s">
         <v>161</v>
       </c>
       <c r="B1" s="9"/>
@@ -2088,444 +1996,444 @@
       <c r="D1" s="9"/>
       <c r="E1" s="9"/>
     </row>
-    <row r="2" spans="1:9" ht="22.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="11" t="s">
+    <row r="2" spans="1:9" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="E2" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="19" t="s">
+      <c r="F2" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="19" t="s">
+      <c r="G2" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="H2" s="19" t="s">
+      <c r="H2" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="I2" s="19" t="s">
+      <c r="I2" s="18" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:9" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="E3" s="14">
+      <c r="B3" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="E3" s="13">
         <v>71.5</v>
       </c>
-      <c r="F3" s="14">
+      <c r="F3" s="13">
         <v>75.3</v>
       </c>
-      <c r="G3" s="14">
+      <c r="G3" s="13">
         <v>72.900000000000006</v>
       </c>
-      <c r="H3" s="14">
+      <c r="H3" s="13">
         <v>70.900000000000006</v>
       </c>
-      <c r="I3" s="14">
+      <c r="I3" s="13">
         <v>69.5</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="18.649999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:9" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="14" t="s">
-        <v>31</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="E4" s="14" t="s">
-        <v>144</v>
-      </c>
-      <c r="F4" s="14">
+      <c r="B4" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>143</v>
+      </c>
+      <c r="F4" s="13">
         <v>81.400000000000006</v>
       </c>
-      <c r="G4" s="14">
+      <c r="G4" s="13">
         <v>79.400000000000006</v>
       </c>
-      <c r="H4" s="14">
+      <c r="H4" s="13">
         <v>77.8</v>
       </c>
-      <c r="I4" s="14">
+      <c r="I4" s="13">
         <v>76.900000000000006</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="27.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:9" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>69</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="F5" s="14">
+      <c r="B5" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="F5" s="13">
         <v>77.7</v>
       </c>
-      <c r="G5" s="14">
+      <c r="G5" s="13">
         <v>75.2</v>
       </c>
-      <c r="H5" s="14">
+      <c r="H5" s="13">
         <v>73.2</v>
       </c>
-      <c r="I5" s="14">
+      <c r="I5" s="13">
         <v>71.8</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="27.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:9" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>71</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>79</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="F6" s="14">
+      <c r="B6" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="F6" s="13">
         <v>73.3</v>
       </c>
-      <c r="G6" s="14">
+      <c r="G6" s="13">
         <v>71.400000000000006</v>
       </c>
-      <c r="H6" s="14">
+      <c r="H6" s="13">
         <v>70</v>
       </c>
-      <c r="I6" s="14">
+      <c r="I6" s="13">
         <v>69.2</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="27.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:9" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>74</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>107</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>146</v>
-      </c>
-      <c r="F7" s="14">
+      <c r="B7" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="F7" s="13">
         <v>89.4</v>
       </c>
-      <c r="G7" s="14">
+      <c r="G7" s="13">
         <v>87.8</v>
       </c>
-      <c r="H7" s="14">
+      <c r="H7" s="13">
         <v>86.8</v>
       </c>
-      <c r="I7" s="14">
+      <c r="I7" s="13">
         <v>86.4</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="27.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:9" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="14" t="s">
-        <v>42</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>77</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="E8" s="14" t="s">
+      <c r="B8" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>25</v>
+      </c>
+      <c r="E8" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="F8" s="13">
         <v>89</v>
       </c>
-      <c r="F8" s="14">
-        <v>89</v>
-      </c>
-      <c r="G8" s="14">
+      <c r="G8" s="13">
         <v>86.8</v>
       </c>
-      <c r="H8" s="14">
+      <c r="H8" s="13">
         <v>85.1</v>
       </c>
-      <c r="I8" s="14">
+      <c r="I8" s="13">
         <v>84.1</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="27.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:9" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B9" s="14" t="s">
-        <v>44</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>147</v>
-      </c>
-      <c r="F9" s="14">
+      <c r="B9" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>146</v>
+      </c>
+      <c r="F9" s="13">
         <v>114.3</v>
       </c>
-      <c r="G9" s="14">
+      <c r="G9" s="13">
         <v>113.5</v>
       </c>
-      <c r="H9" s="14">
+      <c r="H9" s="13">
         <v>113.3</v>
       </c>
-      <c r="I9" s="14">
+      <c r="I9" s="13">
         <v>114</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="27.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:9" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>82</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="F10" s="14">
+      <c r="B10" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="F10" s="13">
         <v>86.6</v>
       </c>
-      <c r="G10" s="14">
+      <c r="G10" s="13">
         <v>83.8</v>
       </c>
-      <c r="H10" s="14">
+      <c r="H10" s="13">
         <v>81.5</v>
       </c>
-      <c r="I10" s="14">
+      <c r="I10" s="13">
         <v>79.900000000000006</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="27.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:9" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B11" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="E11" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="F11" s="14">
+      <c r="B11" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="E11" s="13" t="s">
+        <v>147</v>
+      </c>
+      <c r="F11" s="13">
         <v>85.4</v>
       </c>
-      <c r="G11" s="14">
+      <c r="G11" s="13">
         <v>84</v>
       </c>
-      <c r="H11" s="14">
+      <c r="H11" s="13">
         <v>83.1</v>
       </c>
-      <c r="I11" s="14">
+      <c r="I11" s="13">
         <v>82.9</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="27.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:9" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="14" t="s">
-        <v>51</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>87</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="E12" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="F12" s="14">
+      <c r="B12" s="13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="E12" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="F12" s="13">
         <v>91</v>
       </c>
-      <c r="G12" s="14">
+      <c r="G12" s="13">
         <v>88.1</v>
       </c>
-      <c r="H12" s="14">
+      <c r="H12" s="13">
         <v>85.8</v>
       </c>
-      <c r="I12" s="14">
+      <c r="I12" s="13">
         <v>84.1</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:9" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="14" t="s">
-        <v>53</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>88</v>
-      </c>
-      <c r="D13" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="F13" s="14">
+      <c r="B13" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="C13" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="D13" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="E13" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="F13" s="13">
         <v>84.1</v>
       </c>
-      <c r="G13" s="14">
+      <c r="G13" s="13">
         <v>82.6</v>
       </c>
-      <c r="H13" s="14">
+      <c r="H13" s="13">
         <v>81.5</v>
       </c>
-      <c r="I13" s="14">
+      <c r="I13" s="13">
         <v>81.099999999999994</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="27.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:9" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B14" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>91</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="E14" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="F14" s="14">
+      <c r="B14" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="D14" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="F14" s="13">
         <v>90.3</v>
       </c>
-      <c r="G14" s="14">
+      <c r="G14" s="13">
         <v>86.7</v>
       </c>
-      <c r="H14" s="14">
+      <c r="H14" s="13">
         <v>83.8</v>
       </c>
-      <c r="I14" s="14">
+      <c r="I14" s="13">
         <v>81.5</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="27.5" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:9" ht="27" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="14" t="s">
-        <v>58</v>
-      </c>
-      <c r="C15" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D15" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="E15" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="F15" s="14">
+      <c r="B15" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="F15" s="13">
         <v>89.3</v>
       </c>
-      <c r="G15" s="14">
+      <c r="G15" s="13">
         <v>85.6</v>
       </c>
-      <c r="H15" s="14">
+      <c r="H15" s="13">
         <v>82.5</v>
       </c>
-      <c r="I15" s="14">
+      <c r="I15" s="13">
         <v>80.2</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="27" x14ac:dyDescent="0.35">
-      <c r="A16" s="12" t="s">
+    <row r="16" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
+      <c r="A16" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="C16" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="D16" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="E16" s="17" t="s">
-        <v>127</v>
-      </c>
-      <c r="F16" s="17">
+      <c r="B16" s="16" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>126</v>
+      </c>
+      <c r="F16" s="16">
         <v>84.3</v>
       </c>
-      <c r="G16" s="17">
+      <c r="G16" s="16">
         <v>81.7</v>
       </c>
-      <c r="H16" s="17">
+      <c r="H16" s="16">
         <v>79.62</v>
       </c>
-      <c r="I16" s="17">
+      <c r="I16" s="16">
         <v>78.19</v>
       </c>
     </row>
-    <row r="17" spans="1:1" ht="15.5" x14ac:dyDescent="0.35">
-      <c r="A17" s="10" t="s">
-        <v>25</v>
+    <row r="17" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A17" s="20" t="s">
+        <v>159</v>
       </c>
     </row>
   </sheetData>

--- a/Donnees/Statistiques Démographiques et sociales/Education/Taux Net de Scolarisation 2006-2023.xlsx
+++ b/Donnees/Statistiques Démographiques et sociales/Education/Taux Net de Scolarisation 2006-2023.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\Ansade_Project\Donnees\Statistiques Démographiques et sociales\Education\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{629B80E4-447C-40EE-9513-807C541E49AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16A9361C-30DD-40BB-83EE-9DFA71B06E54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Garçons" sheetId="4" r:id="rId1"/>
